--- a/dati.xlsx
+++ b/dati.xlsx
@@ -16,7 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +453,116 @@
         <is>
           <t>Punti</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>42</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eleonora</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>42</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mara</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
